--- a/PTBR/Lang/PTBR/Game/Faction.xlsx
+++ b/PTBR/Lang/PTBR/Game/Faction.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Lar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -537,11 +537,6 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ホーム</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sua base.</t>
         </is>
       </c>
     </row>
@@ -571,11 +566,6 @@
           <t>野生</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Uma região inexplorada, onde a natureza reina e o perigo espreita.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -603,11 +593,6 @@
           <t>戦士ギルド</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lar dos guerreiros que vivem pela espada e pelo combate.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,11 +620,6 @@
           <t>盗賊ギルド</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Um refúgio sombrio para os que vivem nas sombras.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,11 +647,6 @@
           <t>魔術師ギルド</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Centro arcano de estudo e poder mágico.</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -686,7 +661,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guilda dos Comerciantes</t>
+          <t>Guilda dos Mercadores</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -697,11 +672,6 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>商人ギルド</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Onde riqueza e influência valem mais que espadas.</t>
         </is>
       </c>
     </row>
@@ -731,11 +701,6 @@
           <t>イエル</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Uma vila pacata cercada por mistérios antigos.</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -763,11 +728,6 @@
           <t>エウダーナ</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Cidade ancestral marcada por segredos e magia esquecida.</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -795,11 +755,6 @@
           <t>ヴィンデール</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Terras frias onde o vento carrega histórias de guerra.</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -827,11 +782,6 @@
           <t>ティリス議会</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>A cúpula que governa com sabedoria... E interesses ocultos.</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -859,11 +809,6 @@
           <t>パルミア</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Coração do comércio e das intrigas políticas.</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -889,11 +834,6 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ミシリア</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Uma floresta viva, berço dos espíritos e da antiga magia.</t>
         </is>
       </c>
     </row>
